--- a/Result/profitability/8081.xlsx
+++ b/Result/profitability/8081.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.1</v>
       </c>
       <c r="M2" t="n">
-        <v>4.08625</v>
+        <v>4.04625</v>
       </c>
       <c r="N2" t="n">
-        <v>38.385</v>
+        <v>38.475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.86</v>
       </c>
       <c r="M3" t="n">
-        <v>3.715</v>
+        <v>3.73</v>
       </c>
       <c r="N3" t="n">
-        <v>37.53</v>
+        <v>37.945</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>3.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6225</v>
+        <v>3.585</v>
       </c>
       <c r="N4" t="n">
-        <v>37.3975</v>
+        <v>37.30125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.17</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1675</v>
+        <v>3.27</v>
       </c>
       <c r="N5" t="n">
-        <v>36.16125</v>
+        <v>36.04875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>1.99</v>
       </c>
       <c r="M6" t="n">
-        <v>2.955</v>
+        <v>2.95125</v>
       </c>
       <c r="N6" t="n">
-        <v>34.97875</v>
+        <v>35.62125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>2.55</v>
+        <v>2.525</v>
       </c>
       <c r="N7" t="n">
-        <v>34.83125</v>
+        <v>35.1175</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.77</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3075</v>
+        <v>2.29375</v>
       </c>
       <c r="N8" t="n">
-        <v>34.32875</v>
+        <v>34.42875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8081</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2238</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1333</v>
+      </c>
+      <c r="E75" t="n">
+        <v>904</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="G75" t="n">
+        <v>452</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.18%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>24</v>
+      </c>
+      <c r="J75" t="n">
+        <v>476</v>
+      </c>
+      <c r="K75" t="n">
+        <v>386</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4.512499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.08499999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.1100000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.02380952380952384</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.7999999999999972</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02019691996970452</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8199999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2222222222222221</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9000000000000057</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02178649237472785</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
